--- a/examples/test_cases.xlsx
+++ b/examples/test_cases.xlsx
@@ -1,62 +1,376 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="14860" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="测试用例" sheetId="1" r:id="rId1"/>
+    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="33">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -64,18 +378,378 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -395,157 +1069,427 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6" outlineLevelRow="7"/>
+  <cols>
+    <col width="17.8571428571429" customWidth="1" min="1" max="1"/>
+    <col width="39.7321428571429" customWidth="1" min="2" max="2"/>
+    <col width="11.5982142857143" customWidth="1" min="3" max="3"/>
+    <col width="11.7589285714286" customWidth="1" min="4" max="4"/>
+    <col width="24.1071428571429" customWidth="1" min="5" max="5"/>
+    <col width="103.410714285714" customWidth="1" min="6" max="6"/>
+    <col width="49.5535714285714" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>测试用例ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>测试名称</v>
-      </c>
-      <c r="C1" t="str">
-        <v>测试类型</v>
-      </c>
-      <c r="D1" t="str">
-        <v>优先级</v>
-      </c>
-      <c r="E1" t="str">
-        <v>前置条件</v>
-      </c>
-      <c r="F1" t="str">
-        <v>测试步骤</v>
-      </c>
-      <c r="G1" t="str">
-        <v>预期结果</v>
-      </c>
-      <c r="H1" t="str">
-        <v>测试数据</v>
-      </c>
-      <c r="I1" t="str">
-        <v>任务超时时间</v>
-      </c>
-      <c r="J1" t="str">
-        <v>标签</v>
-      </c>
-      <c r="K1" t="str">
-        <v>设备ID</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>测试用例ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>测试名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>测试类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>测试步骤</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>预期结果</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>任务超时时间</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>设备ID</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>TC-PURCHASE-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>新建采购单</v>
-      </c>
-      <c r="C2" t="str">
-        <v>采购单</v>
-      </c>
-      <c r="D2" t="str">
-        <v>P1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>设备已连接并授权</v>
-      </c>
-      <c r="F2" t="str">
-        <v>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'采购单' ，验证页面底部需要出现“新建采购单”按钮</v>
-      </c>
-      <c r="G2" t="str">
-        <v>验证页面底部出现“新建采购单”按钮</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>150</v>
-      </c>
-      <c r="J2" t="str">
-        <v>smoke</v>
-      </c>
-      <c r="K2" t="str">
-        <v>AFUKUT4926013963</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>检查采购单模块跳转</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>采购单</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'采购单' ，验证页面底部需要出现“新建采购单”按钮</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>验证页面底部出现“新建采购单”按钮</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>TC-SALES-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>新建销售单</v>
-      </c>
-      <c r="C3" t="str">
-        <v>销售单</v>
-      </c>
-      <c r="D3" t="str">
-        <v>P1</v>
-      </c>
-      <c r="E3" t="str">
-        <v>设备已连接并授权</v>
-      </c>
-      <c r="F3" t="str">
-        <v>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'销售单' ，验证页面底部需要出现“新建销售单”按钮</v>
-      </c>
-      <c r="G3" t="str">
-        <v>验证页面底部出现“新建销售单”按钮</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>150</v>
-      </c>
-      <c r="J3" t="str">
-        <v>smoke,regression</v>
-      </c>
-      <c r="K3" t="str">
-        <v>PQY5T20A07017811</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>检查销售单模块跳转</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>销售单</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'销售单' ，验证页面底部需要出现“新建销售单”按钮</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>验证页面底部出现“新建销售单”按钮</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>smoke,regression</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>TC-PURCHASE-002</v>
-      </c>
-      <c r="B4" t="str">
-        <v>新建采购单</v>
-      </c>
-      <c r="C4" t="str">
-        <v>采购单</v>
-      </c>
-      <c r="D4" t="str">
-        <v>P1</v>
-      </c>
-      <c r="E4" t="str">
-        <v>设备已连接并授权</v>
-      </c>
-      <c r="F4" t="str">
-        <v>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'订货单' ，验证页面底部需要出现“新建工厂”按钮</v>
-      </c>
-      <c r="G4" t="str">
-        <v>验证页面底部出现“新建采购单”按钮</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>150</v>
-      </c>
-      <c r="J4" t="str">
-        <v>smoke</v>
-      </c>
-      <c r="K4" t="str">
-        <v>AFUKUT4926013963</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>检查订货单模块跳转</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>订货单</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'订货单' ，验证页面底部需要出现“新建订货单”按钮</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>验证页面底部出现“新建订货单”按钮</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>检查采购单模块跳转</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>预订单</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'预订单' ，验证页面底部需要出现“新建预订单”按钮</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>验证页面底部出现“新建预订单”按钮</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>检查发货单模块跳转</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>发货单</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'发货单' ，验证页面底部需要出现“新建发货单”按钮</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>验证页面底部出现“新建发货单”按钮</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>检查必失败用例</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>采购单</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.打开森果产地通app 2.点击底部'加工厂'按钮 3.点击'采购单' ，验证页面底部需要出现“进入淘宝”按钮</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>验证页面底部出现“进入淘宝”按钮</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="106" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>检查新增采购单流程</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>采购单</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>设备已连接并授权</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>打开”森果产地通“的app，点击底部的“加工厂”按钮后，停留3秒，点击”采购单“，
+点击底部”新建采购单“，选择“苹果”分类，选择农户“非伍6”，下滑页面，点击“选择货
+品”按钮，点击“称重苹果3”下面的“采购规格1”，点击“数量”框，点击输入1，点击“毛
+重”，点击2，停留2秒，点击“单价”框，点击4，点击“折扣金额”，输入1，点击“确认”按钮，点击
+“去结算”，点击“按采收规格定价”，点击“赊账待付”，点击“确认结算”，检查在采购单列表页面，有新的采购单数据生成</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>验证采购单列表页面，出现了一条新农户为”非伍6“的采购单数据</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>180</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>